--- a/data/trans_dic/IP12B$fiebre-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$fiebre-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por fiebre</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor por fiebre (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,11</t>
+          <t>0,0; 64,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,93</t>
+          <t>0,0; 25,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 59,94</t>
+          <t>0,0; 61,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,57</t>
+          <t>0,0; 50,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,14</t>
+          <t>0,0; 37,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 18,4</t>
+          <t>0,0; 17,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,29</t>
+          <t>0,0; 49,37</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,55</t>
+          <t>0,0; 12,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,84; 23,13</t>
+          <t>4,27; 23,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,87; 24,38</t>
+          <t>5,51; 24,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,16; 22,98</t>
+          <t>4,04; 22,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,79; 32,02</t>
+          <t>10,6; 32,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,12; 30,27</t>
+          <t>9,18; 30,08</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,19; 14,4</t>
+          <t>3,13; 13,73</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,49; 23,98</t>
+          <t>10,28; 24,85</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,11; 23,57</t>
+          <t>9,66; 23,56</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,08</t>
+          <t>0,0; 36,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,01; 41,88</t>
+          <t>8,12; 42,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,92</t>
+          <t>3,2; 32,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,98</t>
+          <t>0,0; 38,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,63</t>
+          <t>0,0; 26,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,04</t>
+          <t>0,0; 38,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,31; 24,76</t>
+          <t>3,33; 27,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,96; 28,2</t>
+          <t>6,56; 28,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,77; 26,46</t>
+          <t>4,77; 27,62</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,44; 13,36</t>
+          <t>1,51; 13,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,14; 21,85</t>
+          <t>6,89; 21,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,74; 22,62</t>
+          <t>7,51; 23,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,35; 20,06</t>
+          <t>5,35; 19,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,62; 27,04</t>
+          <t>8,93; 25,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,29; 26,81</t>
+          <t>9,32; 26,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,38; 13,62</t>
+          <t>4,37; 14,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,37; 20,15</t>
+          <t>9,51; 20,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,97; 20,8</t>
+          <t>9,25; 20,59</t>
         </is>
       </c>
     </row>
@@ -1071,4 +1072,791 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor por fiebre (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1395</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1372</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1395</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3665</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2560</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4062</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2799</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4153</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2975</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4354</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1220</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4032</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4261</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3281</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>9327</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>6439</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>4501</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>13359</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>10700</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3803</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1495; 8151</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1753; 7792</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1265; 6898</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>4799; 14700</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>3339; 10940</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1905; 8371</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>8259; 19966</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>6585; 16065</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>674</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>3396</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1914</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1251</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>697</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1317</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1925</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>4093</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>3230</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3147</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1315; 6878</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>535; 5379</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3828</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2938</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3530</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>614; 5006</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>1797; 7723</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1238; 7174</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2564</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>8010</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7570</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5233</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>10024</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>7756</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>7798</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>18034</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>15325</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>663; 5848</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>4221; 13253</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>4141; 12848</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2498; 9219</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>5674; 16080</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>4462; 12443</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>3959; 12714</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>11872; 25853</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>9521; 21208</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$fiebre-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$fiebre-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por fiebre (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por fiebre (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,12 +678,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,82</t>
+          <t>0,0; 62,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,45</t>
+          <t>0,0; 24,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,85</t>
+          <t>0,0; 52,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,22</t>
+          <t>0,0; 31,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,39</t>
+          <t>0,0; 16,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,37</t>
+          <t>0,0; 43,53</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,84</t>
+          <t>0,0; 14,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,27; 23,26</t>
+          <t>4,37; 23,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,51; 24,49</t>
+          <t>5,72; 24,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,04; 22,0</t>
+          <t>4,0; 22,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,6; 32,45</t>
+          <t>11,61; 32,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,18; 30,08</t>
+          <t>9,92; 28,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,13; 13,73</t>
+          <t>3,13; 13,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,28; 24,85</t>
+          <t>10,0; 24,91</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,66; 23,56</t>
+          <t>9,93; 23,49</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,6</t>
+          <t>0,0; 38,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,12; 42,51</t>
+          <t>8,18; 42,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,2; 32,16</t>
+          <t>2,97; 29,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,84</t>
+          <t>0,0; 39,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,19</t>
+          <t>0,0; 33,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,17</t>
+          <t>0,0; 38,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,33; 27,13</t>
+          <t>3,33; 28,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,56; 28,19</t>
+          <t>7,04; 28,82</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,77; 27,62</t>
+          <t>4,67; 27,31</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 13,33</t>
+          <t>1,51; 14,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,89; 21,62</t>
+          <t>6,78; 20,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,51; 23,31</t>
+          <t>7,36; 22,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,35; 19,74</t>
+          <t>5,49; 20,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,93; 25,3</t>
+          <t>8,06; 24,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,32; 26,0</t>
+          <t>9,11; 26,71</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,37; 14,04</t>
+          <t>4,96; 14,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,51; 20,71</t>
+          <t>9,88; 20,91</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,25; 20,59</t>
+          <t>10,26; 20,5</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor por fiebre (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor por fiebre (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,12 +1306,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3665</t>
+          <t>0; 3505</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2560</t>
+          <t>0; 2434</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2799</t>
+          <t>0; 2872</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1336,17 +1336,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4153</t>
+          <t>0; 3538</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2975</t>
+          <t>0; 2793</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 4354</t>
+          <t>0; 3839</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3803</t>
+          <t>0; 4223</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1495; 8151</t>
+          <t>1531; 8100</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1753; 7792</t>
+          <t>1821; 7863</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1265; 6898</t>
+          <t>1254; 7173</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4799; 14700</t>
+          <t>5258; 14926</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3339; 10940</t>
+          <t>3609; 10434</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1905; 8371</t>
+          <t>1911; 8516</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8259; 19966</t>
+          <t>8035; 20013</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6585; 16065</t>
+          <t>6773; 16015</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3147</t>
+          <t>0; 3325</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1315; 6878</t>
+          <t>1323; 6879</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>535; 5379</t>
+          <t>497; 4970</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3828</t>
+          <t>0; 3858</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 2938</t>
+          <t>0; 3806</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3530</t>
+          <t>0; 3520</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>614; 5006</t>
+          <t>614; 5257</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1797; 7723</t>
+          <t>1929; 7895</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1238; 7174</t>
+          <t>1212; 7094</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>663; 5848</t>
+          <t>661; 6276</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4221; 13253</t>
+          <t>4156; 12806</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4141; 12848</t>
+          <t>4059; 12160</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2498; 9219</t>
+          <t>2566; 9752</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5674; 16080</t>
+          <t>5124; 15427</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4462; 12443</t>
+          <t>4358; 12783</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3959; 12714</t>
+          <t>4495; 12777</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11872; 25853</t>
+          <t>12336; 26100</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>9521; 21208</t>
+          <t>10561; 21110</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$fiebre-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$fiebre-Estudios-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>12,75%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>11,86%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>5,78%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>21,2%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12,75%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,0</t>
+          <t>0,0; 60,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,18</t>
+          <t>0,0; 62,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 30,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 59,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,72</t>
+          <t>0,0; 34,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,33</t>
+          <t>0,0; 18,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,53</t>
+          <t>0,0; 46,29</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>10,47%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>20,59%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>17,7%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>4,12%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>11,5%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>13,39%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>10,47%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>20,59%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>17,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,26</t>
+          <t>4,16; 22,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,37; 23,11</t>
+          <t>10,79; 32,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,72; 24,71</t>
+          <t>10,12; 30,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,0; 22,88</t>
+          <t>0,0; 12,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,61; 32,95</t>
+          <t>3,84; 23,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,92; 28,69</t>
+          <t>5,87; 24,38</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,13; 13,97</t>
+          <t>3,19; 14,4</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,0; 24,91</t>
+          <t>10,49; 23,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,93; 23,49</t>
+          <t>9,11; 23,57</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>12,69%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>6,21%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>14,24%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>7,84%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>20,99%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>11,44%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>12,69%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>6,21%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>14,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,68</t>
+          <t>0,0; 38,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,18; 42,51</t>
+          <t>0,0; 28,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,97; 29,72</t>
+          <t>0,0; 45,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,14</t>
+          <t>0,0; 35,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,93</t>
+          <t>8,01; 41,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,07</t>
+          <t>0,0; 26,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,33; 28,49</t>
+          <t>3,31; 24,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,04; 28,82</t>
+          <t>4,96; 28,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,67; 27,31</t>
+          <t>4,77; 26,46</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11,2%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>15,77%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>16,21%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>5,84%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>13,07%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>13,73%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11,2%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>15,77%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>16,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,51; 14,3</t>
+          <t>5,35; 20,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,78; 20,89</t>
+          <t>9,62; 27,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,36; 22,06</t>
+          <t>9,29; 26,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,49; 20,88</t>
+          <t>1,44; 13,36</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,06; 24,27</t>
+          <t>7,14; 21,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,11; 26,71</t>
+          <t>7,74; 22,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,96; 14,11</t>
+          <t>4,38; 13,62</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,88; 20,91</t>
+          <t>9,37; 20,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>10,26; 20,5</t>
+          <t>9,97; 20,8</t>
         </is>
       </c>
     </row>
@@ -1105,14 +1105,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1205,27 +1205,27 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>670</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>582</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>1395</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>702</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3505</t>
+          <t>0; 3334</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2434</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 4062</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2872</t>
+          <t>0; 3511</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3112</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3944</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3538</t>
+          <t>0; 3810</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2793</t>
+          <t>0; 3148</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3839</t>
+          <t>0; 4082</t>
         </is>
       </c>
     </row>
@@ -1363,32 +1363,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1416,32 +1416,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3281</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>9327</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6439</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1220</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>4032</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>4261</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3281</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>9327</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>6439</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4223</t>
+          <t>1306; 7204</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1531; 8100</t>
+          <t>4887; 14505</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1821; 7863</t>
+          <t>3680; 11009</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1254; 7173</t>
+          <t>0; 3718</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>5258; 14926</t>
+          <t>1347; 8107</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3609; 10434</t>
+          <t>1866; 7758</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1911; 8516</t>
+          <t>1944; 8782</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>8035; 20013</t>
+          <t>8429; 19270</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>6773; 16015</t>
+          <t>6214; 16073</t>
         </is>
       </c>
     </row>
@@ -1526,32 +1526,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1579,32 +1579,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1251</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>697</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1317</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>674</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>3396</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>1914</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1251</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>697</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1317</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3325</t>
+          <t>0; 3842</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1323; 6879</t>
+          <t>0; 3211</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>497; 4970</t>
+          <t>0; 4165</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 3858</t>
+          <t>0; 3016</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3806</t>
+          <t>1296; 6776</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3520</t>
+          <t>0; 4503</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>614; 5257</t>
+          <t>610; 4570</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1929; 7895</t>
+          <t>1358; 7727</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1212; 7094</t>
+          <t>1240; 6872</t>
         </is>
       </c>
     </row>
@@ -1689,27 +1689,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>11</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5233</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>10024</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7756</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>2564</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>8010</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>7570</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5233</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>10024</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7756</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>661; 6276</t>
+          <t>2501; 9368</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4156; 12806</t>
+          <t>6114; 17188</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4059; 12160</t>
+          <t>4446; 12831</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2566; 9752</t>
+          <t>632; 5862</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5124; 15427</t>
+          <t>4374; 13392</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4358; 12783</t>
+          <t>4268; 12467</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4495; 12777</t>
+          <t>3964; 12340</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12336; 26100</t>
+          <t>11696; 25154</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10561; 21110</t>
+          <t>10270; 21420</t>
         </is>
       </c>
     </row>
